--- a/ig/DM-SEPTEMBRE-2026/ValueSet-jdv-resultat-depistage-crp-cisis.xlsx
+++ b/ig/DM-SEPTEMBRE-2026/ValueSet-jdv-resultat-depistage-crp-cisis.xlsx
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20260716085851</t>
+    <t>20260916095452</t>
   </si>
   <si>
     <t>Name</t>
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-16T08:58:51+01:00</t>
+    <t>2026-09-16T09:54:52+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -99,22 +99,22 @@
     <t>Concept</t>
   </si>
   <si>
-    <t>260385009</t>
-  </si>
-  <si>
-    <t>négatif(-ive)</t>
-  </si>
-  <si>
-    <t>10828004</t>
-  </si>
-  <si>
-    <t>positif(-ive)</t>
-  </si>
-  <si>
-    <t>373068000</t>
-  </si>
-  <si>
-    <t>indéterminé(e)</t>
+    <t>NEG</t>
+  </si>
+  <si>
+    <t>Négatif</t>
+  </si>
+  <si>
+    <t>POS</t>
+  </si>
+  <si>
+    <t>Positif</t>
+  </si>
+  <si>
+    <t>IND</t>
+  </si>
+  <si>
+    <t>Indéterminé</t>
   </si>
   <si>
     <t/>
@@ -123,7 +123,7 @@
     <t>System URI</t>
   </si>
   <si>
-    <t>http://snomed.info/sct</t>
+    <t>http://terminology.hl7.org/CodeSystem/v3-ObservationInterpretation</t>
   </si>
 </sst>
 </file>
